--- a/outputs/documentos_caracterizados_muestra.xlsx
+++ b/outputs/documentos_caracterizados_muestra.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>doc_0153</t>
+          <t>doc_0020</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>doc_0154</t>
+          <t>doc_0021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>doc_0156</t>
+          <t>doc_0023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>doc_0155</t>
+          <t>doc_0022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>doc_0157</t>
+          <t>doc_0024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>doc_0158</t>
+          <t>doc_0025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>doc_0159</t>
+          <t>doc_0026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>doc_0160</t>
+          <t>doc_0027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>doc_0161</t>
+          <t>doc_0028</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>doc_0162</t>
+          <t>doc_0029</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>doc_0165</t>
+          <t>doc_0032</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>doc_0163</t>
+          <t>doc_0030</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>doc_0164</t>
+          <t>doc_0031</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>doc_0166</t>
+          <t>doc_0033</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>doc_0167</t>
+          <t>doc_0034</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>doc_0168</t>
+          <t>doc_0035</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>doc_0169</t>
+          <t>doc_0036</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>doc_0170</t>
+          <t>doc_0037</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>doc_0172</t>
+          <t>doc_0039</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>doc_0171</t>
+          <t>doc_0038</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>doc_0275</t>
+          <t>doc_0142</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2101,7 +2101,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>doc_0280</t>
+          <t>doc_0147</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>doc_0289</t>
+          <t>doc_0156</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>doc_0290</t>
+          <t>doc_0157</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>doc_0291</t>
+          <t>doc_0158</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>doc_0292</t>
+          <t>doc_0159</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>doc_0293</t>
+          <t>doc_0160</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>doc_0295</t>
+          <t>doc_0162</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>doc_0298</t>
+          <t>doc_0165</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>doc_0312</t>
+          <t>doc_0179</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
